--- a/test_data_template.xlsx
+++ b/test_data_template.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="数据管理" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'数据管理'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,19 +431,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -510,32 +510,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/data/2026Q1/annotation_01.json</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>v3.2.0</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ADAS标注集</t>
+          <t>/data/2026Q2/case_001.json</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>多模工具</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>感知</t>
+          <t>多意图</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>车道线检测</t>
+          <t>NLU解析</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>labelme</t>
+          <t>nlu_parser</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -543,15 +543,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TAG_003: 多轮上下文丢失</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -561,48 +565,48 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/data/2026Q1/annotation_02.json</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>v3.2.0</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ADAS标注集</t>
+          <t>/data/2026Q2/case_002.json</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>干扰图</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>感知</t>
+          <t>多轮对话</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>障碍物检测</t>
+          <t>ASR识别</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>labelme</t>
+          <t>asr_tool</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -612,32 +616,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>/data/2026Q1/lidar_001.pcd</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>v3.2.0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>激光雷达点云</t>
+          <t>/data/2026Q2/case_003.json</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>干扰图</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>明确意图</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>目标跟踪</t>
+          <t>结果反馈</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>manual_tag</t>
+          <t>task_runner</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -645,14 +649,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TAG_001: 目标丢失</t>
+          <t>TAG_002: 意图理解偏差</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,42 +671,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>/data/2026Q2/camera_01.png</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>v3.3.0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>前视摄像头</t>
+          <t>/data/2026Q2/case_004.json</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>robot-phone</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>感知</t>
+          <t>多轮对话</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>交通标志识别</t>
+          <t>意图澄清</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>auto_tag</t>
+          <t>intent_cls</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -718,32 +722,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/data/2026Q2/camera_02.png</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>v3.3.0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>前视摄像头</t>
+          <t>/data/2026Q2/case_005.json</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>域外工具</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>感知</t>
+          <t>模糊意图</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>红绿灯识别</t>
+          <t>意图澄清</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>auto_tag</t>
+          <t>intent_cls</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -751,14 +755,14 @@
           <t>否</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>TAG_002: 误检</t>
+          <t>TAG_003: 多轮上下文丢失</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -773,52 +777,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/data/2026Q2/radar_01.bin</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>v3.3.0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>毫米波雷达</t>
+          <t>/data/2026Q2/case_006.json</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>域外工具</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>模糊意图</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>目标检测</t>
+          <t>结果反馈</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>manual_tag</t>
+          <t>intent_cls</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>TAG_003: 数据缺失</t>
+          <t>TAG_003: 多轮上下文丢失</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -828,42 +832,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/data/2026Q2/lidar_002.pcd</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>v3.3.1</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>激光雷达点云</t>
+          <t>/data/2026Q2/case_007.json</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>robot-phone</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>多意图</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SLAM建图</t>
+          <t>ASR识别</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>slam_tool</t>
+          <t>nlu_parser</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -879,32 +883,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/data/2026Q3/annotation_03.json</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>v3.3.1</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>ADAS标注集</t>
+          <t>/data/2026Q2/case_008.json</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>robot-phone</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>规控</t>
+          <t>多意图</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>路径规划</t>
+          <t>意图澄清</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>labelme</t>
+          <t>nlu_parser</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -912,14 +916,14 @@
           <t>否</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>TAG_004: 路径偏移</t>
+          <t>TAG_002: 意图理解偏差</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,32 +938,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>/data/2026Q3/camera_03.png</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>v3.4.0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>环视摄像头</t>
+          <t>/data/2026Q2/case_009.json</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>robot-phone</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>感知</t>
+          <t>多轮对话</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>车位检测</t>
+          <t>任务执行</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>auto_tag</t>
+          <t>intent_cls</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -967,9 +971,9 @@
           <t>是</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -985,50 +989,584 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/data/2026Q3/imu_01.csv</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>v3.4.0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>IMU数据</t>
+          <t>/data/2026Q2/case_010.json</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>通用工具</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>定位</t>
+          <t>多轮对话</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>姿态估计</t>
+          <t>意图澄清</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>imu_calib</t>
+          <t>asr_tool</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>TAG_005: 漂移超限</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_011.json</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>域外工具</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>明确意图</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>意图澄清</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nlu_parser</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TAG_003: 多轮上下文丢失</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_012.json</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>干扰图</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>多轮对话</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>意图澄清</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nlu_parser</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_013.json</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>robot-phone</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>明确意图</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>任务执行</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>reply_gen</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TAG_001: ASR识别错误</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_014.json</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>干扰图</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>多意图</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>结果反馈</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>asr_tool</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TAG_003: 多轮上下文丢失</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_015.json</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>通用工具</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>多轮对话</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NLU解析</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>task_runner</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TAG_002: 意图理解偏差</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_016.json</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>通用工具</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>明确意图</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NLU解析</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>intent_cls</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TAG_002: 意图理解偏差</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_017.json</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>多模工具</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>模糊意图</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>意图澄清</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>intent_cls</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_018.json</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>多模工具</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>多轮对话</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ASR识别</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>reply_gen</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>TAG_003: 多轮上下文丢失</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_019.json</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>通用工具</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>多轮对话</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NLU解析</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>reply_gen</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TAG_001: ASR识别错误</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>/data/2026Q2/case_020.json</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>干扰图</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>多轮对话</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ASR识别</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>nlu_parser</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>

--- a/test_data_template.xlsx
+++ b/test_data_template.xlsx
@@ -2,37 +2,95 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="时延与Token分析" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$S$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +99,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -54,11 +124,104 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -66,9 +229,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -431,20 +622,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Y21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" style="8" min="1" max="1"/>
+    <col width="38" customWidth="1" style="8" min="2" max="2"/>
+    <col width="10" customWidth="1" style="8" min="3" max="3"/>
+    <col width="14" customWidth="1" style="8" min="4" max="4"/>
+    <col width="12" customWidth="1" style="8" min="5" max="6"/>
+    <col width="14" customWidth="1" style="8" min="7" max="7"/>
+    <col width="12" customWidth="1" style="8" min="8" max="8"/>
+    <col width="18" customWidth="1" style="8" min="9" max="9"/>
+    <col width="26" customWidth="1" style="8" min="10" max="10"/>
+    <col width="12" customWidth="1" style="8" min="11" max="11"/>
+    <col width="13.6328125" customWidth="1" style="8" min="12" max="12"/>
+    <col width="14" customWidth="1" style="8" min="13" max="13"/>
+    <col width="12.1796875" customWidth="1" style="8" min="14" max="14"/>
+    <col width="12.26953125" customWidth="1" style="8" min="15" max="15"/>
+    <col width="13.26953125" customWidth="1" style="8" min="16" max="16"/>
+    <col width="14.1796875" customWidth="1" style="8" min="17" max="17"/>
+    <col width="11.08984375" customWidth="1" style="8" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,7 +697,77 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>model_version_v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>first_latency_ms_v4.3_简单</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>first_input_tokens_v4.3_简单</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>first_output_tokens_v4.3_简单</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>last_latency_ms_v4.3_简单</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>last_input_tokens_v4.3_简单</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>last_output_tokens_v4.3_简单</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>不纳入统计</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>model_version_v4.3_复杂</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>first_latency_ms_v4.3_复杂</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>first_input_tokens_v4.3_复杂</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>first_output_tokens_v4.3_复杂</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>last_latency_ms_v4.3_复杂</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>last_input_tokens_v4.3_复杂</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>last_output_tokens_v4.3_复杂</t>
         </is>
       </c>
     </row>
@@ -553,10 +820,56 @@
           <t>TAG_003: 多轮上下文丢失</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>60</v>
+      </c>
+      <c r="O2" t="n">
+        <v>900</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>50</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>v4.3_复杂</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W2" t="n">
+        <v>900</v>
+      </c>
+      <c r="X2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -603,11 +916,56 @@
           <t>合理</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="N3" t="n">
+        <v>62</v>
+      </c>
+      <c r="O3" t="n">
+        <v>950</v>
+      </c>
+      <c r="P3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>51</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>v4.4_复杂</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="U3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="V3" t="n">
+        <v>62</v>
+      </c>
+      <c r="W3" t="n">
+        <v>950</v>
+      </c>
+      <c r="X3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -659,10 +1017,56 @@
           <t>TAG_002: 意图理解偏差</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>64</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>52</v>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>v4.5_复杂</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>64</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -709,11 +1113,56 @@
           <t>合理</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8500</v>
+      </c>
+      <c r="N5" t="n">
+        <v>66</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1050</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>53</v>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>v4.6_复杂</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8500</v>
+      </c>
+      <c r="V5" t="n">
+        <v>66</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1050</v>
+      </c>
+      <c r="X5" t="n">
+        <v>11000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -765,10 +1214,56 @@
           <t>TAG_003: 多轮上下文丢失</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>68</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>54</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>v4.7_复杂</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>68</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="X6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -820,10 +1315,56 @@
           <t>TAG_003: 多轮上下文丢失</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9500</v>
+      </c>
+      <c r="N7" t="n">
+        <v>70</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>55</v>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>v4.8_复杂</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9500</v>
+      </c>
+      <c r="V7" t="n">
+        <v>70</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1150</v>
+      </c>
+      <c r="X7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -870,11 +1411,56 @@
           <t>不合理</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>72</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>56</v>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>v4.9_复杂</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>72</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="X8" t="n">
+        <v>14000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -926,10 +1512,56 @@
           <t>TAG_002: 意图理解偏差</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1700</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10500</v>
+      </c>
+      <c r="N9" t="n">
+        <v>74</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1250</v>
+      </c>
+      <c r="P9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>57</v>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>v4.10_复杂</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>1700</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10500</v>
+      </c>
+      <c r="V9" t="n">
+        <v>74</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1250</v>
+      </c>
+      <c r="X9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -976,11 +1608,56 @@
           <t>不合理</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>76</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1300</v>
+      </c>
+      <c r="P10" t="n">
+        <v>16000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>58</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>v4.11_复杂</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U10" t="n">
+        <v>11000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>76</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1300</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -1027,11 +1704,56 @@
           <t>不合理</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11500</v>
+      </c>
+      <c r="N11" t="n">
+        <v>78</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1350</v>
+      </c>
+      <c r="P11" t="n">
+        <v>17000</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>59</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>v4.12_复杂</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>1900</v>
+      </c>
+      <c r="U11" t="n">
+        <v>11500</v>
+      </c>
+      <c r="V11" t="n">
+        <v>78</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1350</v>
+      </c>
+      <c r="X11" t="n">
+        <v>17000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -1083,10 +1805,56 @@
           <t>TAG_003: 多轮上下文丢失</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="N12" t="n">
+        <v>80</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P12" t="n">
+        <v>18000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>60</v>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>v4.13_复杂</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>80</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="X12" t="n">
+        <v>18000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -1133,11 +1901,56 @@
           <t>不合理</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2100</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12500</v>
+      </c>
+      <c r="N13" t="n">
+        <v>82</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1450</v>
+      </c>
+      <c r="P13" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>61</v>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>v4.14_复杂</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>2100</v>
+      </c>
+      <c r="U13" t="n">
+        <v>12500</v>
+      </c>
+      <c r="V13" t="n">
+        <v>82</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1450</v>
+      </c>
+      <c r="X13" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -1189,10 +2002,56 @@
           <t>TAG_001: ASR识别错误</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>13000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>84</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>62</v>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>v4.15_复杂</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>2200</v>
+      </c>
+      <c r="U14" t="n">
+        <v>13000</v>
+      </c>
+      <c r="V14" t="n">
+        <v>84</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="X14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -1244,10 +2103,56 @@
           <t>TAG_003: 多轮上下文丢失</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2300</v>
+      </c>
+      <c r="M15" t="n">
+        <v>13500</v>
+      </c>
+      <c r="N15" t="n">
+        <v>86</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1550</v>
+      </c>
+      <c r="P15" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>63</v>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>v4.16_复杂</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>2300</v>
+      </c>
+      <c r="U15" t="n">
+        <v>13500</v>
+      </c>
+      <c r="V15" t="n">
+        <v>86</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1550</v>
+      </c>
+      <c r="X15" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1299,10 +2204,56 @@
           <t>TAG_002: 意图理解偏差</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>88</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="P16" t="n">
+        <v>22000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>64</v>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>v4.17_复杂</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14000</v>
+      </c>
+      <c r="V16" t="n">
+        <v>88</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="X16" t="n">
+        <v>22000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1354,10 +2305,56 @@
           <t>TAG_002: 意图理解偏差</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14500</v>
+      </c>
+      <c r="N17" t="n">
+        <v>90</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1650</v>
+      </c>
+      <c r="P17" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>65</v>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>v4.18_复杂</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>2500</v>
+      </c>
+      <c r="U17" t="n">
+        <v>14500</v>
+      </c>
+      <c r="V17" t="n">
+        <v>90</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1650</v>
+      </c>
+      <c r="X17" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -1404,11 +2401,56 @@
           <t>合理</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2600</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="N18" t="n">
+        <v>92</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1700</v>
+      </c>
+      <c r="P18" t="n">
+        <v>24000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>66</v>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>v4.19_复杂</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>2600</v>
+      </c>
+      <c r="U18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="V18" t="n">
+        <v>92</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1700</v>
+      </c>
+      <c r="X18" t="n">
+        <v>24000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -1460,10 +2502,56 @@
           <t>TAG_003: 多轮上下文丢失</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2700</v>
+      </c>
+      <c r="M19" t="n">
+        <v>15500</v>
+      </c>
+      <c r="N19" t="n">
+        <v>94</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1750</v>
+      </c>
+      <c r="P19" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>67</v>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>v4.20_复杂</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>2700</v>
+      </c>
+      <c r="U19" t="n">
+        <v>15500</v>
+      </c>
+      <c r="V19" t="n">
+        <v>94</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1750</v>
+      </c>
+      <c r="X19" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1515,10 +2603,56 @@
           <t>TAG_001: ASR识别错误</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2800</v>
+      </c>
+      <c r="M20" t="n">
+        <v>16000</v>
+      </c>
+      <c r="N20" t="n">
+        <v>96</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="P20" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>68</v>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>v4.21_复杂</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>2800</v>
+      </c>
+      <c r="U20" t="n">
+        <v>16000</v>
+      </c>
+      <c r="V20" t="n">
+        <v>96</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="X20" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="21">
@@ -1565,15 +2699,540 @@
           <t>合理</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>2900</v>
+      </c>
+      <c r="M21" t="n">
+        <v>16500</v>
+      </c>
+      <c r="N21" t="n">
+        <v>98</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1850</v>
+      </c>
+      <c r="P21" t="n">
+        <v>27000</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>69</v>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>v4.22_复杂</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>2900</v>
+      </c>
+      <c r="U21" t="n">
+        <v>16500</v>
+      </c>
+      <c r="V21" t="n">
+        <v>98</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1850</v>
+      </c>
+      <c r="X21" t="n">
+        <v>27000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:S1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="8" min="1" max="1"/>
+    <col width="10" customWidth="1" style="8" min="2" max="2"/>
+    <col width="10" customWidth="1" style="8" min="3" max="3"/>
+    <col width="10" customWidth="1" style="8" min="4" max="4"/>
+    <col width="10" customWidth="1" style="8" min="5" max="5"/>
+    <col width="10" customWidth="1" style="8" min="6" max="6"/>
+    <col width="10" customWidth="1" style="8" min="7" max="7"/>
+    <col width="10" customWidth="1" style="8" min="8" max="8"/>
+    <col width="10" customWidth="1" style="8" min="9" max="9"/>
+    <col width="10" customWidth="1" style="8" min="10" max="10"/>
+    <col width="10" customWidth="1" style="8" min="11" max="11"/>
+    <col width="10" customWidth="1" style="8" min="12" max="12"/>
+    <col width="10" customWidth="1" style="8" min="13" max="13"/>
+    <col width="10" customWidth="1" style="8" min="14" max="14"/>
+    <col width="10" customWidth="1" style="8" min="15" max="15"/>
+    <col width="10" customWidth="1" style="8" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="8">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>v4.3_简单</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n"/>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>时延(ms)</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>输入token</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>输出token</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>均值</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>P95</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>均值</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>P95</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>均值</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>首轮</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>2425</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>2710</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>2805</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>11750</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>11750</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>14125</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>15550</v>
+      </c>
+      <c r="K4" s="12" t="n">
+        <v>16025</v>
+      </c>
+      <c r="L4" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="M4" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="N4" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="O4" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="P4" s="12" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>最后一轮</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>1375</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>1612</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1755</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>17500</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>17500</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>22250</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>25100</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>26050</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="N5" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="P5" s="12" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" s="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>v4.3_复杂</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>时延(ms)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>输入token</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>输出token</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>均值</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>P95</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>均值</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>P95</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>均值</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>首轮</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>2425</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>2710</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>2805</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>11750</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>11750</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>14125</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>15550</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>16025</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="N11" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="O11" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="P11" s="12" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>最后一轮</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>1375</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>1612</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>1755</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>17500</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>17500</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>22250</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>25100</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>26050</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="N12" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="O12" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="P12" s="12" t="n">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="L9:P9"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="A8:P8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="G9:K9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>